--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -3867,10 +3867,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822538</v>
+        <v>119822540</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3883,21 +3883,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461306</v>
+        <v>461816</v>
       </c>
       <c r="R32" t="n">
-        <v>7064614</v>
+        <v>7065029</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3943,11 +3943,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3974,7 +3969,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822506</v>
+        <v>119822538</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -4014,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461650</v>
+        <v>461306</v>
       </c>
       <c r="R33" t="n">
-        <v>7064593</v>
+        <v>7064614</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4081,10 +4076,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822540</v>
+        <v>119822506</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4097,21 +4092,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4121,10 +4116,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461816</v>
+        <v>461650</v>
       </c>
       <c r="R34" t="n">
-        <v>7065029</v>
+        <v>7064593</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4157,6 +4152,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822533</v>
+        <v>119822542</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461336</v>
+        <v>461534</v>
       </c>
       <c r="R2" t="n">
-        <v>7064553</v>
+        <v>7064335</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822536</v>
+        <v>119822520</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461326</v>
+        <v>461287</v>
       </c>
       <c r="R3" t="n">
-        <v>7064600</v>
+        <v>7064267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822529</v>
+        <v>119822500</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461336</v>
+        <v>461569</v>
       </c>
       <c r="R4" t="n">
-        <v>7064457</v>
+        <v>7065017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822541</v>
+        <v>119822508</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461873</v>
+        <v>461571</v>
       </c>
       <c r="R5" t="n">
-        <v>7065016</v>
+        <v>7064490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822511</v>
+        <v>119822533</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461559</v>
+        <v>461336</v>
       </c>
       <c r="R6" t="n">
-        <v>7064334</v>
+        <v>7064553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822528</v>
+        <v>119822522</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461314</v>
+        <v>461156</v>
       </c>
       <c r="R7" t="n">
-        <v>7064456</v>
+        <v>7064289</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822507</v>
+        <v>119822506</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461560</v>
+        <v>461650</v>
       </c>
       <c r="R8" t="n">
-        <v>7064491</v>
+        <v>7064593</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822526</v>
+        <v>119822505</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461252</v>
+        <v>461847</v>
       </c>
       <c r="R9" t="n">
-        <v>7064479</v>
+        <v>7064897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822502</v>
+        <v>119822524</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461858</v>
+        <v>461256</v>
       </c>
       <c r="R10" t="n">
-        <v>7065038</v>
+        <v>7064474</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822524</v>
+        <v>119822503</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461256</v>
+        <v>461856</v>
       </c>
       <c r="R11" t="n">
-        <v>7064474</v>
+        <v>7065027</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822500</v>
+        <v>119822515</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461569</v>
+        <v>461455</v>
       </c>
       <c r="R12" t="n">
-        <v>7065017</v>
+        <v>7064272</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822539</v>
+        <v>119822529</v>
       </c>
       <c r="B13" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,20 +1859,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1880,29 +1880,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461525</v>
+        <v>461336</v>
       </c>
       <c r="R13" t="n">
-        <v>7064452</v>
+        <v>7064457</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1961,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822542</v>
+        <v>119822540</v>
       </c>
       <c r="B14" t="n">
         <v>90580</v>
@@ -2001,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461534</v>
+        <v>461816</v>
       </c>
       <c r="R14" t="n">
-        <v>7064335</v>
+        <v>7065029</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822520</v>
+        <v>119822498</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2103,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461287</v>
+        <v>461417</v>
       </c>
       <c r="R15" t="n">
-        <v>7064267</v>
+        <v>7064708</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822545</v>
+        <v>119822523</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2210,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461589</v>
+        <v>461217</v>
       </c>
       <c r="R16" t="n">
-        <v>7064542</v>
+        <v>7064345</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,6 +2239,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2272,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822522</v>
+        <v>119822514</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2312,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461156</v>
+        <v>461475</v>
       </c>
       <c r="R17" t="n">
-        <v>7064289</v>
+        <v>7064279</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2379,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822508</v>
+        <v>119822513</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2419,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461571</v>
+        <v>461492</v>
       </c>
       <c r="R18" t="n">
-        <v>7064490</v>
+        <v>7064272</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2486,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822499</v>
+        <v>119822530</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2526,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461452</v>
+        <v>461353</v>
       </c>
       <c r="R19" t="n">
-        <v>7064801</v>
+        <v>7064480</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822516</v>
+        <v>119822527</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2633,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461443</v>
+        <v>461315</v>
       </c>
       <c r="R20" t="n">
-        <v>7064240</v>
+        <v>7064474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822509</v>
+        <v>119822499</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2740,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461603</v>
+        <v>461452</v>
       </c>
       <c r="R21" t="n">
-        <v>7064451</v>
+        <v>7064801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822497</v>
+        <v>119822501</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2823,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2847,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461316</v>
+        <v>461668</v>
       </c>
       <c r="R22" t="n">
-        <v>7064356</v>
+        <v>7065012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,6 +2881,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2909,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822498</v>
+        <v>119822541</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2925,21 +2928,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461417</v>
+        <v>461873</v>
       </c>
       <c r="R23" t="n">
-        <v>7064708</v>
+        <v>7065016</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,11 +2988,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3016,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822517</v>
+        <v>119822507</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3056,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461341</v>
+        <v>461560</v>
       </c>
       <c r="R24" t="n">
-        <v>7064286</v>
+        <v>7064491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,7 +3094,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3123,7 +3121,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822515</v>
+        <v>119822536</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3163,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461455</v>
+        <v>461326</v>
       </c>
       <c r="R25" t="n">
-        <v>7064272</v>
+        <v>7064600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3203,7 +3201,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3230,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822518</v>
+        <v>119822504</v>
       </c>
       <c r="B26" t="n">
         <v>57310</v>
@@ -3270,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461326</v>
+        <v>461951</v>
       </c>
       <c r="R26" t="n">
-        <v>7064274</v>
+        <v>7064993</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,7 +3335,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822504</v>
+        <v>119822518</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3377,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461951</v>
+        <v>461326</v>
       </c>
       <c r="R27" t="n">
-        <v>7064993</v>
+        <v>7064274</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822543</v>
+        <v>119822516</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3460,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461512</v>
+        <v>461443</v>
       </c>
       <c r="R28" t="n">
-        <v>7064795</v>
+        <v>7064240</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3520,6 +3518,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3546,7 +3549,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822521</v>
+        <v>119822531</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3586,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461214</v>
+        <v>461347</v>
       </c>
       <c r="R29" t="n">
-        <v>7064209</v>
+        <v>7064491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,7 +3629,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3653,7 +3656,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822514</v>
+        <v>119822521</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3693,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461475</v>
+        <v>461214</v>
       </c>
       <c r="R30" t="n">
-        <v>7064279</v>
+        <v>7064209</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3733,7 +3736,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3760,7 +3763,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822510</v>
+        <v>119822528</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3800,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461551</v>
+        <v>461314</v>
       </c>
       <c r="R31" t="n">
-        <v>7064346</v>
+        <v>7064456</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3840,7 +3843,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,10 +3870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822540</v>
+        <v>119822543</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3883,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461816</v>
+        <v>461512</v>
       </c>
       <c r="R32" t="n">
-        <v>7065029</v>
+        <v>7064795</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,10 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822538</v>
+        <v>119822539</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3981,20 +3984,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4002,17 +4005,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461306</v>
+        <v>461525</v>
       </c>
       <c r="R33" t="n">
-        <v>7064614</v>
+        <v>7064452</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4045,11 +4060,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4076,7 +4086,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822506</v>
+        <v>119822535</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4116,10 +4126,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461650</v>
+        <v>461326</v>
       </c>
       <c r="R34" t="n">
-        <v>7064593</v>
+        <v>7064610</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4156,7 +4166,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4183,7 +4193,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822503</v>
+        <v>119822519</v>
       </c>
       <c r="B35" t="n">
         <v>57310</v>
@@ -4223,10 +4233,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461856</v>
+        <v>461301</v>
       </c>
       <c r="R35" t="n">
-        <v>7065027</v>
+        <v>7064270</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4263,7 +4273,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4290,10 +4300,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822505</v>
+        <v>119822497</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4306,21 +4316,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4330,10 +4340,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461847</v>
+        <v>461316</v>
       </c>
       <c r="R36" t="n">
-        <v>7064897</v>
+        <v>7064356</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4366,11 +4376,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4397,7 +4402,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822535</v>
+        <v>119822538</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4437,10 +4442,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461326</v>
+        <v>461306</v>
       </c>
       <c r="R37" t="n">
-        <v>7064610</v>
+        <v>7064614</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4477,7 +4482,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4504,7 +4509,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822534</v>
+        <v>119822537</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4544,10 +4549,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461337</v>
+        <v>461313</v>
       </c>
       <c r="R38" t="n">
-        <v>7064589</v>
+        <v>7064604</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4584,7 +4589,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4611,7 +4616,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822519</v>
+        <v>119822517</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4651,10 +4656,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461301</v>
+        <v>461341</v>
       </c>
       <c r="R39" t="n">
-        <v>7064270</v>
+        <v>7064286</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4691,7 +4696,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,7 +4723,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822527</v>
+        <v>119822511</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4758,10 +4763,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461315</v>
+        <v>461559</v>
       </c>
       <c r="R40" t="n">
-        <v>7064474</v>
+        <v>7064334</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4825,10 +4830,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822537</v>
+        <v>119822544</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4841,21 +4846,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4865,10 +4870,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461313</v>
+        <v>461853</v>
       </c>
       <c r="R41" t="n">
-        <v>7064604</v>
+        <v>7064648</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4901,11 +4906,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4932,10 +4932,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822523</v>
+        <v>119822545</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4948,21 +4948,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461217</v>
+        <v>461589</v>
       </c>
       <c r="R42" t="n">
-        <v>7064345</v>
+        <v>7064542</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5008,11 +5008,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5039,7 +5034,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822513</v>
+        <v>119822526</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5079,10 +5074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461492</v>
+        <v>461252</v>
       </c>
       <c r="R43" t="n">
-        <v>7064272</v>
+        <v>7064479</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5119,7 +5114,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,7 +5141,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822531</v>
+        <v>119822534</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5186,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461347</v>
+        <v>461337</v>
       </c>
       <c r="R44" t="n">
-        <v>7064491</v>
+        <v>7064589</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5226,7 +5221,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5253,7 +5248,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822530</v>
+        <v>119822510</v>
       </c>
       <c r="B45" t="n">
         <v>57310</v>
@@ -5293,10 +5288,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461353</v>
+        <v>461551</v>
       </c>
       <c r="R45" t="n">
-        <v>7064480</v>
+        <v>7064346</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5333,7 +5328,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5360,7 +5355,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822501</v>
+        <v>119822509</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5400,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461668</v>
+        <v>461603</v>
       </c>
       <c r="R46" t="n">
-        <v>7065012</v>
+        <v>7064451</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5467,10 +5462,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822544</v>
+        <v>119822502</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5483,21 +5478,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5507,10 +5502,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461853</v>
+        <v>461858</v>
       </c>
       <c r="R47" t="n">
-        <v>7064648</v>
+        <v>7065038</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5543,6 +5538,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -3972,10 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822539</v>
+        <v>119822535</v>
       </c>
       <c r="B33" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3984,20 +3984,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4005,29 +4005,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461525</v>
+        <v>461326</v>
       </c>
       <c r="R33" t="n">
-        <v>7064452</v>
+        <v>7064610</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,6 +4048,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4086,7 +4079,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822535</v>
+        <v>119822519</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4126,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461326</v>
+        <v>461301</v>
       </c>
       <c r="R34" t="n">
-        <v>7064610</v>
+        <v>7064270</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4166,7 +4159,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4193,10 +4186,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822519</v>
+        <v>119822539</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4205,20 +4198,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4226,17 +4219,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461301</v>
+        <v>461525</v>
       </c>
       <c r="R35" t="n">
-        <v>7064270</v>
+        <v>7064452</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4269,11 +4274,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4509,10 +4509,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822537</v>
+        <v>119822544</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4525,21 +4525,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461313</v>
+        <v>461853</v>
       </c>
       <c r="R38" t="n">
-        <v>7064604</v>
+        <v>7064648</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4585,11 +4585,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4616,7 +4611,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822517</v>
+        <v>119822537</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4656,10 +4651,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461341</v>
+        <v>461313</v>
       </c>
       <c r="R39" t="n">
-        <v>7064286</v>
+        <v>7064604</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4696,7 +4691,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4723,7 +4718,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822511</v>
+        <v>119822517</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4763,10 +4758,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461559</v>
+        <v>461341</v>
       </c>
       <c r="R40" t="n">
-        <v>7064334</v>
+        <v>7064286</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,7 +4798,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4830,10 +4825,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822544</v>
+        <v>119822511</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4846,21 +4841,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4870,10 +4865,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461853</v>
+        <v>461559</v>
       </c>
       <c r="R41" t="n">
-        <v>7064648</v>
+        <v>7064334</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4906,6 +4901,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822542</v>
+        <v>119822522</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461534</v>
+        <v>461156</v>
       </c>
       <c r="R2" t="n">
-        <v>7064335</v>
+        <v>7064289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822520</v>
+        <v>119822542</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461287</v>
+        <v>461534</v>
       </c>
       <c r="R3" t="n">
-        <v>7064267</v>
+        <v>7064335</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822500</v>
+        <v>119822541</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461569</v>
+        <v>461873</v>
       </c>
       <c r="R4" t="n">
-        <v>7065017</v>
+        <v>7065016</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822508</v>
+        <v>119822545</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461571</v>
+        <v>461589</v>
       </c>
       <c r="R5" t="n">
-        <v>7064490</v>
+        <v>7064542</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822533</v>
+        <v>119822523</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1138,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461336</v>
+        <v>461217</v>
       </c>
       <c r="R6" t="n">
-        <v>7064553</v>
+        <v>7064345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822522</v>
+        <v>119822513</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461156</v>
+        <v>461492</v>
       </c>
       <c r="R7" t="n">
-        <v>7064289</v>
+        <v>7064272</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822506</v>
+        <v>119822535</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1352,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461650</v>
+        <v>461326</v>
       </c>
       <c r="R8" t="n">
-        <v>7064593</v>
+        <v>7064610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822505</v>
+        <v>119822531</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1459,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461847</v>
+        <v>461347</v>
       </c>
       <c r="R9" t="n">
-        <v>7064897</v>
+        <v>7064491</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822524</v>
+        <v>119822527</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1566,7 +1556,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461256</v>
+        <v>461315</v>
       </c>
       <c r="R10" t="n">
         <v>7064474</v>
@@ -1633,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822503</v>
+        <v>119822507</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1673,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461856</v>
+        <v>461560</v>
       </c>
       <c r="R11" t="n">
-        <v>7065027</v>
+        <v>7064491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822515</v>
+        <v>119822536</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1780,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461455</v>
+        <v>461326</v>
       </c>
       <c r="R12" t="n">
-        <v>7064272</v>
+        <v>7064600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822529</v>
+        <v>119822498</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1887,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461336</v>
+        <v>461417</v>
       </c>
       <c r="R13" t="n">
-        <v>7064457</v>
+        <v>7064708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822498</v>
+        <v>119822537</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2096,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461417</v>
+        <v>461313</v>
       </c>
       <c r="R15" t="n">
-        <v>7064708</v>
+        <v>7064604</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822523</v>
+        <v>119822538</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2203,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461217</v>
+        <v>461306</v>
       </c>
       <c r="R16" t="n">
-        <v>7064345</v>
+        <v>7064614</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822514</v>
+        <v>119822506</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2310,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461475</v>
+        <v>461650</v>
       </c>
       <c r="R17" t="n">
-        <v>7064279</v>
+        <v>7064593</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822513</v>
+        <v>119822502</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2417,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461492</v>
+        <v>461858</v>
       </c>
       <c r="R18" t="n">
-        <v>7064272</v>
+        <v>7065038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822530</v>
+        <v>119822514</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2524,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461353</v>
+        <v>461475</v>
       </c>
       <c r="R19" t="n">
-        <v>7064480</v>
+        <v>7064279</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822527</v>
+        <v>119822528</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2631,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461315</v>
+        <v>461314</v>
       </c>
       <c r="R20" t="n">
-        <v>7064474</v>
+        <v>7064456</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822499</v>
+        <v>119822508</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2738,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461452</v>
+        <v>461571</v>
       </c>
       <c r="R21" t="n">
-        <v>7064801</v>
+        <v>7064490</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2768,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822501</v>
+        <v>119822543</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461668</v>
+        <v>461512</v>
       </c>
       <c r="R22" t="n">
-        <v>7065012</v>
+        <v>7064795</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,11 +2871,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822541</v>
+        <v>119822520</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461873</v>
+        <v>461287</v>
       </c>
       <c r="R23" t="n">
-        <v>7065016</v>
+        <v>7064267</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,6 +2973,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3004,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822507</v>
+        <v>119822529</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3054,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461560</v>
+        <v>461336</v>
       </c>
       <c r="R24" t="n">
-        <v>7064491</v>
+        <v>7064457</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3084,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822536</v>
+        <v>119822505</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3161,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461326</v>
+        <v>461847</v>
       </c>
       <c r="R25" t="n">
-        <v>7064600</v>
+        <v>7064897</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3191,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,7 +3218,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822504</v>
+        <v>119822509</v>
       </c>
       <c r="B26" t="n">
         <v>57310</v>
@@ -3268,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461951</v>
+        <v>461603</v>
       </c>
       <c r="R26" t="n">
-        <v>7064993</v>
+        <v>7064451</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822518</v>
+        <v>119822539</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3347,20 +3337,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3368,17 +3358,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461326</v>
+        <v>461525</v>
       </c>
       <c r="R27" t="n">
-        <v>7064274</v>
+        <v>7064452</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,11 +3413,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,7 +3439,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822516</v>
+        <v>119822521</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3482,10 +3479,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461443</v>
+        <v>461214</v>
       </c>
       <c r="R28" t="n">
-        <v>7064240</v>
+        <v>7064209</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3549,7 +3546,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822531</v>
+        <v>119822504</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3589,10 +3586,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461347</v>
+        <v>461951</v>
       </c>
       <c r="R29" t="n">
-        <v>7064491</v>
+        <v>7064993</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3656,7 +3653,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822521</v>
+        <v>119822500</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3696,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461214</v>
+        <v>461569</v>
       </c>
       <c r="R30" t="n">
-        <v>7064209</v>
+        <v>7065017</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3733,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,7 +3760,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822528</v>
+        <v>119822499</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3803,10 +3800,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461314</v>
+        <v>461452</v>
       </c>
       <c r="R31" t="n">
-        <v>7064456</v>
+        <v>7064801</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,10 +3867,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822543</v>
+        <v>119822526</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,21 +3883,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461512</v>
+        <v>461252</v>
       </c>
       <c r="R32" t="n">
-        <v>7064795</v>
+        <v>7064479</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3946,6 +3943,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,7 +3974,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822535</v>
+        <v>119822515</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -4012,10 +4014,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461326</v>
+        <v>461455</v>
       </c>
       <c r="R33" t="n">
-        <v>7064610</v>
+        <v>7064272</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4052,7 +4054,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,7 +4081,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822519</v>
+        <v>119822534</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4119,10 +4121,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461301</v>
+        <v>461337</v>
       </c>
       <c r="R34" t="n">
-        <v>7064270</v>
+        <v>7064589</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4159,7 +4161,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4186,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822539</v>
+        <v>119822524</v>
       </c>
       <c r="B35" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4198,20 +4200,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4219,29 +4221,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461525</v>
+        <v>461256</v>
       </c>
       <c r="R35" t="n">
-        <v>7064452</v>
+        <v>7064474</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,6 +4264,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4300,10 +4295,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822497</v>
+        <v>119822501</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4316,21 +4311,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4340,10 +4335,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461316</v>
+        <v>461668</v>
       </c>
       <c r="R36" t="n">
-        <v>7064356</v>
+        <v>7065012</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4376,6 +4371,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4402,7 +4402,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822538</v>
+        <v>119822516</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461306</v>
+        <v>461443</v>
       </c>
       <c r="R37" t="n">
-        <v>7064614</v>
+        <v>7064240</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4509,10 +4509,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822544</v>
+        <v>119822533</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4525,21 +4525,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461853</v>
+        <v>461336</v>
       </c>
       <c r="R38" t="n">
-        <v>7064648</v>
+        <v>7064553</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4585,6 +4585,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4611,7 +4616,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822537</v>
+        <v>119822519</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4651,10 +4656,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461313</v>
+        <v>461301</v>
       </c>
       <c r="R39" t="n">
-        <v>7064604</v>
+        <v>7064270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4691,7 +4696,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,7 +4723,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822517</v>
+        <v>119822530</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4758,10 +4763,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461341</v>
+        <v>461353</v>
       </c>
       <c r="R40" t="n">
-        <v>7064286</v>
+        <v>7064480</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4825,10 +4830,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822511</v>
+        <v>119822497</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4841,21 +4846,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4865,10 +4870,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461559</v>
+        <v>461316</v>
       </c>
       <c r="R41" t="n">
-        <v>7064334</v>
+        <v>7064356</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4901,11 +4906,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4932,10 +4932,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822545</v>
+        <v>119822511</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4948,21 +4948,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461589</v>
+        <v>461559</v>
       </c>
       <c r="R42" t="n">
-        <v>7064542</v>
+        <v>7064334</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5008,6 +5008,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5034,7 +5039,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822526</v>
+        <v>119822518</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5074,10 +5079,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461252</v>
+        <v>461326</v>
       </c>
       <c r="R43" t="n">
-        <v>7064479</v>
+        <v>7064274</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5141,7 +5146,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822534</v>
+        <v>119822510</v>
       </c>
       <c r="B44" t="n">
         <v>57310</v>
@@ -5181,10 +5186,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461337</v>
+        <v>461551</v>
       </c>
       <c r="R44" t="n">
-        <v>7064589</v>
+        <v>7064346</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5248,10 +5253,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822510</v>
+        <v>119822544</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5264,21 +5269,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5288,10 +5293,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461551</v>
+        <v>461853</v>
       </c>
       <c r="R45" t="n">
-        <v>7064346</v>
+        <v>7064648</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5324,11 +5329,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5355,7 +5355,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822509</v>
+        <v>119822517</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461603</v>
+        <v>461341</v>
       </c>
       <c r="R46" t="n">
-        <v>7064451</v>
+        <v>7064286</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5462,7 +5462,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822502</v>
+        <v>119822503</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461858</v>
+        <v>461856</v>
       </c>
       <c r="R47" t="n">
-        <v>7065038</v>
+        <v>7065027</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822541</v>
+        <v>119822545</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461873</v>
+        <v>461589</v>
       </c>
       <c r="R4" t="n">
-        <v>7065016</v>
+        <v>7064542</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822545</v>
+        <v>119822507</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461589</v>
+        <v>461560</v>
       </c>
       <c r="R5" t="n">
-        <v>7064542</v>
+        <v>7064491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822523</v>
+        <v>119822536</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461217</v>
+        <v>461326</v>
       </c>
       <c r="R6" t="n">
-        <v>7064345</v>
+        <v>7064600</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822513</v>
+        <v>119822523</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461492</v>
+        <v>461217</v>
       </c>
       <c r="R7" t="n">
-        <v>7064272</v>
+        <v>7064345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822535</v>
+        <v>119822513</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461326</v>
+        <v>461492</v>
       </c>
       <c r="R8" t="n">
-        <v>7064610</v>
+        <v>7064272</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822531</v>
+        <v>119822527</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461347</v>
+        <v>461315</v>
       </c>
       <c r="R9" t="n">
-        <v>7064491</v>
+        <v>7064474</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822527</v>
+        <v>119822535</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461315</v>
+        <v>461326</v>
       </c>
       <c r="R10" t="n">
-        <v>7064474</v>
+        <v>7064610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822507</v>
+        <v>119822531</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1663,7 +1668,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461560</v>
+        <v>461347</v>
       </c>
       <c r="R11" t="n">
         <v>7064491</v>
@@ -1703,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822536</v>
+        <v>119822541</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461326</v>
+        <v>461873</v>
       </c>
       <c r="R12" t="n">
-        <v>7064600</v>
+        <v>7065016</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -4402,7 +4402,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822516</v>
+        <v>119822533</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461443</v>
+        <v>461336</v>
       </c>
       <c r="R37" t="n">
-        <v>7064240</v>
+        <v>7064553</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4509,7 +4509,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822533</v>
+        <v>119822516</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461336</v>
+        <v>461443</v>
       </c>
       <c r="R38" t="n">
-        <v>7064553</v>
+        <v>7064240</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822522</v>
+        <v>119822507</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461156</v>
+        <v>461560</v>
       </c>
       <c r="R2" t="n">
-        <v>7064289</v>
+        <v>7064491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822542</v>
+        <v>119822514</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461534</v>
+        <v>461475</v>
       </c>
       <c r="R3" t="n">
-        <v>7064335</v>
+        <v>7064279</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822545</v>
+        <v>119822533</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461589</v>
+        <v>461336</v>
       </c>
       <c r="R4" t="n">
-        <v>7064542</v>
+        <v>7064553</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822507</v>
+        <v>119822526</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461560</v>
+        <v>461252</v>
       </c>
       <c r="R5" t="n">
-        <v>7064491</v>
+        <v>7064479</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822536</v>
+        <v>119822544</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461326</v>
+        <v>461853</v>
       </c>
       <c r="R6" t="n">
-        <v>7064600</v>
+        <v>7064648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822523</v>
+        <v>119822509</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461217</v>
+        <v>461603</v>
       </c>
       <c r="R7" t="n">
-        <v>7064345</v>
+        <v>7064451</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822513</v>
+        <v>119822535</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461492</v>
+        <v>461326</v>
       </c>
       <c r="R8" t="n">
-        <v>7064272</v>
+        <v>7064610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822527</v>
+        <v>119822530</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461315</v>
+        <v>461353</v>
       </c>
       <c r="R9" t="n">
-        <v>7064474</v>
+        <v>7064480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822535</v>
+        <v>119822510</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461326</v>
+        <v>461551</v>
       </c>
       <c r="R10" t="n">
-        <v>7064610</v>
+        <v>7064346</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822531</v>
+        <v>119822528</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461347</v>
+        <v>461314</v>
       </c>
       <c r="R11" t="n">
-        <v>7064491</v>
+        <v>7064456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822541</v>
+        <v>119822536</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461873</v>
+        <v>461326</v>
       </c>
       <c r="R12" t="n">
-        <v>7065016</v>
+        <v>7064600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822498</v>
+        <v>119822502</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1877,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461417</v>
+        <v>461858</v>
       </c>
       <c r="R13" t="n">
-        <v>7064708</v>
+        <v>7065038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822540</v>
+        <v>119822515</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461816</v>
+        <v>461455</v>
       </c>
       <c r="R14" t="n">
-        <v>7065029</v>
+        <v>7064272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,6 +2030,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822537</v>
+        <v>119822503</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2086,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461313</v>
+        <v>461856</v>
       </c>
       <c r="R15" t="n">
-        <v>7064604</v>
+        <v>7065027</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822538</v>
+        <v>119822537</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2193,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461306</v>
+        <v>461313</v>
       </c>
       <c r="R16" t="n">
-        <v>7064614</v>
+        <v>7064604</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822506</v>
+        <v>119822521</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2300,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461650</v>
+        <v>461214</v>
       </c>
       <c r="R17" t="n">
-        <v>7064593</v>
+        <v>7064209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822502</v>
+        <v>119822508</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2407,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461858</v>
+        <v>461571</v>
       </c>
       <c r="R18" t="n">
-        <v>7065038</v>
+        <v>7064490</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822514</v>
+        <v>119822520</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2514,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461475</v>
+        <v>461287</v>
       </c>
       <c r="R19" t="n">
-        <v>7064279</v>
+        <v>7064267</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822528</v>
+        <v>119822499</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2621,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461314</v>
+        <v>461452</v>
       </c>
       <c r="R20" t="n">
-        <v>7064456</v>
+        <v>7064801</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822508</v>
+        <v>119822498</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2728,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461571</v>
+        <v>461417</v>
       </c>
       <c r="R21" t="n">
-        <v>7064490</v>
+        <v>7064708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822543</v>
+        <v>119822522</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461512</v>
+        <v>461156</v>
       </c>
       <c r="R22" t="n">
-        <v>7064795</v>
+        <v>7064289</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,6 +2886,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,7 +2917,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822520</v>
+        <v>119822531</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2937,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461287</v>
+        <v>461347</v>
       </c>
       <c r="R23" t="n">
-        <v>7064267</v>
+        <v>7064491</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822529</v>
+        <v>119822542</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3020,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3044,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461336</v>
+        <v>461534</v>
       </c>
       <c r="R24" t="n">
-        <v>7064457</v>
+        <v>7064335</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3080,11 +3100,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3111,7 +3126,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822505</v>
+        <v>119822517</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3151,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461847</v>
+        <v>461341</v>
       </c>
       <c r="R25" t="n">
-        <v>7064897</v>
+        <v>7064286</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3206,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,10 +3233,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822509</v>
+        <v>119822545</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,21 +3249,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3258,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461603</v>
+        <v>461589</v>
       </c>
       <c r="R26" t="n">
-        <v>7064451</v>
+        <v>7064542</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3309,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822539</v>
+        <v>119822529</v>
       </c>
       <c r="B27" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,20 +3347,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3358,29 +3368,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461525</v>
+        <v>461336</v>
       </c>
       <c r="R27" t="n">
-        <v>7064452</v>
+        <v>7064457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,6 +3411,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,7 +3442,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822521</v>
+        <v>119822519</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3479,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461214</v>
+        <v>461301</v>
       </c>
       <c r="R28" t="n">
-        <v>7064209</v>
+        <v>7064270</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3519,7 +3522,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3546,7 +3549,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822504</v>
+        <v>119822516</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3586,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461951</v>
+        <v>461443</v>
       </c>
       <c r="R29" t="n">
-        <v>7064993</v>
+        <v>7064240</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,7 +3629,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3653,7 +3656,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822500</v>
+        <v>119822513</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3693,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461569</v>
+        <v>461492</v>
       </c>
       <c r="R30" t="n">
-        <v>7065017</v>
+        <v>7064272</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3733,7 +3736,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3760,7 +3763,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822499</v>
+        <v>119822523</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3800,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461452</v>
+        <v>461217</v>
       </c>
       <c r="R31" t="n">
-        <v>7064801</v>
+        <v>7064345</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3840,7 +3843,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,7 +3870,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822526</v>
+        <v>119822501</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3907,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461252</v>
+        <v>461668</v>
       </c>
       <c r="R32" t="n">
-        <v>7064479</v>
+        <v>7065012</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3974,7 +3977,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822515</v>
+        <v>119822518</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -4014,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461455</v>
+        <v>461326</v>
       </c>
       <c r="R33" t="n">
-        <v>7064272</v>
+        <v>7064274</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4054,7 +4057,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4081,10 +4084,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822534</v>
+        <v>119822541</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4097,21 +4100,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4121,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461337</v>
+        <v>461873</v>
       </c>
       <c r="R34" t="n">
-        <v>7064589</v>
+        <v>7065016</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4157,11 +4160,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4188,7 +4186,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822524</v>
+        <v>119822506</v>
       </c>
       <c r="B35" t="n">
         <v>57310</v>
@@ -4228,10 +4226,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461256</v>
+        <v>461650</v>
       </c>
       <c r="R35" t="n">
-        <v>7064474</v>
+        <v>7064593</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822501</v>
+        <v>119822497</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4311,21 +4309,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4335,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461668</v>
+        <v>461316</v>
       </c>
       <c r="R36" t="n">
-        <v>7065012</v>
+        <v>7064356</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4371,11 +4369,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4402,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822533</v>
+        <v>119822543</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4418,21 +4411,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4442,10 +4435,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461336</v>
+        <v>461512</v>
       </c>
       <c r="R37" t="n">
-        <v>7064553</v>
+        <v>7064795</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4478,11 +4471,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4509,7 +4497,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822516</v>
+        <v>119822534</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4549,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461443</v>
+        <v>461337</v>
       </c>
       <c r="R38" t="n">
-        <v>7064240</v>
+        <v>7064589</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4616,7 +4604,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822519</v>
+        <v>119822538</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4656,10 +4644,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461301</v>
+        <v>461306</v>
       </c>
       <c r="R39" t="n">
-        <v>7064270</v>
+        <v>7064614</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4696,7 +4684,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4723,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822530</v>
+        <v>119822540</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4739,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4763,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461353</v>
+        <v>461816</v>
       </c>
       <c r="R40" t="n">
-        <v>7064480</v>
+        <v>7065029</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4799,11 +4787,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4830,10 +4813,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822497</v>
+        <v>119822500</v>
       </c>
       <c r="B41" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4846,21 +4829,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4870,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461316</v>
+        <v>461569</v>
       </c>
       <c r="R41" t="n">
-        <v>7064356</v>
+        <v>7065017</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4906,6 +4889,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4932,7 +4920,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822511</v>
+        <v>119822505</v>
       </c>
       <c r="B42" t="n">
         <v>57310</v>
@@ -4972,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461559</v>
+        <v>461847</v>
       </c>
       <c r="R42" t="n">
-        <v>7064334</v>
+        <v>7064897</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5039,7 +5027,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822518</v>
+        <v>119822524</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5079,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461326</v>
+        <v>461256</v>
       </c>
       <c r="R43" t="n">
-        <v>7064274</v>
+        <v>7064474</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5146,10 +5134,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822510</v>
+        <v>119822539</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5158,20 +5146,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5179,17 +5167,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461551</v>
+        <v>461525</v>
       </c>
       <c r="R44" t="n">
-        <v>7064346</v>
+        <v>7064452</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5222,11 +5222,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5253,10 +5248,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822544</v>
+        <v>119822504</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5269,21 +5264,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5293,10 +5288,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461853</v>
+        <v>461951</v>
       </c>
       <c r="R45" t="n">
-        <v>7064648</v>
+        <v>7064993</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5329,6 +5324,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5355,7 +5355,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822517</v>
+        <v>119822511</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461341</v>
+        <v>461559</v>
       </c>
       <c r="R46" t="n">
-        <v>7064286</v>
+        <v>7064334</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5462,7 +5462,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822503</v>
+        <v>119822527</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461856</v>
+        <v>461315</v>
       </c>
       <c r="R47" t="n">
-        <v>7065027</v>
+        <v>7064474</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822503</v>
+        <v>119822521</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461856</v>
+        <v>461214</v>
       </c>
       <c r="R15" t="n">
-        <v>7065027</v>
+        <v>7064209</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822537</v>
+        <v>119822503</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461313</v>
+        <v>461856</v>
       </c>
       <c r="R16" t="n">
-        <v>7064604</v>
+        <v>7065027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822521</v>
+        <v>119822537</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461214</v>
+        <v>461313</v>
       </c>
       <c r="R17" t="n">
-        <v>7064209</v>
+        <v>7064604</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3335,7 +3335,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822529</v>
+        <v>119822516</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461336</v>
+        <v>461443</v>
       </c>
       <c r="R27" t="n">
-        <v>7064457</v>
+        <v>7064240</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822519</v>
+        <v>119822529</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461301</v>
+        <v>461336</v>
       </c>
       <c r="R28" t="n">
-        <v>7064270</v>
+        <v>7064457</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,7 +3549,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822516</v>
+        <v>119822519</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461443</v>
+        <v>461301</v>
       </c>
       <c r="R29" t="n">
-        <v>7064240</v>
+        <v>7064270</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4813,7 +4813,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822500</v>
+        <v>119822505</v>
       </c>
       <c r="B41" t="n">
         <v>57310</v>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461569</v>
+        <v>461847</v>
       </c>
       <c r="R41" t="n">
-        <v>7065017</v>
+        <v>7064897</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,7 +4920,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822505</v>
+        <v>119822524</v>
       </c>
       <c r="B42" t="n">
         <v>57310</v>
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461847</v>
+        <v>461256</v>
       </c>
       <c r="R42" t="n">
-        <v>7064897</v>
+        <v>7064474</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822524</v>
+        <v>119822500</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461256</v>
+        <v>461569</v>
       </c>
       <c r="R43" t="n">
-        <v>7064474</v>
+        <v>7065017</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822544</v>
+        <v>119822509</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461853</v>
+        <v>461603</v>
       </c>
       <c r="R6" t="n">
-        <v>7064648</v>
+        <v>7064451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822509</v>
+        <v>119822535</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461603</v>
+        <v>461326</v>
       </c>
       <c r="R7" t="n">
-        <v>7064451</v>
+        <v>7064610</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822535</v>
+        <v>119822530</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461326</v>
+        <v>461353</v>
       </c>
       <c r="R8" t="n">
-        <v>7064610</v>
+        <v>7064480</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822530</v>
+        <v>119822544</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461353</v>
+        <v>461853</v>
       </c>
       <c r="R9" t="n">
-        <v>7064480</v>
+        <v>7064648</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822521</v>
+        <v>119822503</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461214</v>
+        <v>461856</v>
       </c>
       <c r="R15" t="n">
-        <v>7064209</v>
+        <v>7065027</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822503</v>
+        <v>119822537</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461856</v>
+        <v>461313</v>
       </c>
       <c r="R16" t="n">
-        <v>7065027</v>
+        <v>7064604</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822537</v>
+        <v>119822521</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461313</v>
+        <v>461214</v>
       </c>
       <c r="R17" t="n">
-        <v>7064604</v>
+        <v>7064209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3335,7 +3335,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822516</v>
+        <v>119822529</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461443</v>
+        <v>461336</v>
       </c>
       <c r="R27" t="n">
-        <v>7064240</v>
+        <v>7064457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822529</v>
+        <v>119822519</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461336</v>
+        <v>461301</v>
       </c>
       <c r="R28" t="n">
-        <v>7064457</v>
+        <v>7064270</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,7 +3549,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822519</v>
+        <v>119822516</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461301</v>
+        <v>461443</v>
       </c>
       <c r="R29" t="n">
-        <v>7064270</v>
+        <v>7064240</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4813,7 +4813,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822505</v>
+        <v>119822500</v>
       </c>
       <c r="B41" t="n">
         <v>57310</v>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461847</v>
+        <v>461569</v>
       </c>
       <c r="R41" t="n">
-        <v>7064897</v>
+        <v>7065017</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,7 +4920,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822524</v>
+        <v>119822505</v>
       </c>
       <c r="B42" t="n">
         <v>57310</v>
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461256</v>
+        <v>461847</v>
       </c>
       <c r="R42" t="n">
-        <v>7064474</v>
+        <v>7064897</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822500</v>
+        <v>119822524</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461569</v>
+        <v>461256</v>
       </c>
       <c r="R43" t="n">
-        <v>7065017</v>
+        <v>7064474</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822503</v>
+        <v>119822521</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461856</v>
+        <v>461214</v>
       </c>
       <c r="R15" t="n">
-        <v>7065027</v>
+        <v>7064209</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822537</v>
+        <v>119822503</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461313</v>
+        <v>461856</v>
       </c>
       <c r="R16" t="n">
-        <v>7064604</v>
+        <v>7065027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822521</v>
+        <v>119822537</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461214</v>
+        <v>461313</v>
       </c>
       <c r="R17" t="n">
-        <v>7064209</v>
+        <v>7064604</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2703,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822498</v>
+        <v>119822542</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461417</v>
+        <v>461534</v>
       </c>
       <c r="R21" t="n">
-        <v>7064708</v>
+        <v>7064335</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2779,11 +2779,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822522</v>
+        <v>119822498</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2850,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461156</v>
+        <v>461417</v>
       </c>
       <c r="R22" t="n">
-        <v>7064289</v>
+        <v>7064708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822531</v>
+        <v>119822522</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2957,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461347</v>
+        <v>461156</v>
       </c>
       <c r="R23" t="n">
-        <v>7064491</v>
+        <v>7064289</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822542</v>
+        <v>119822531</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3040,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461534</v>
+        <v>461347</v>
       </c>
       <c r="R24" t="n">
-        <v>7064335</v>
+        <v>7064491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,6 +3095,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822539</v>
+        <v>119822511</v>
       </c>
       <c r="B44" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5167,29 +5167,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461525</v>
+        <v>461559</v>
       </c>
       <c r="R44" t="n">
-        <v>7064452</v>
+        <v>7064334</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5222,6 +5210,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5248,7 +5241,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822504</v>
+        <v>119822527</v>
       </c>
       <c r="B45" t="n">
         <v>57310</v>
@@ -5288,10 +5281,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461951</v>
+        <v>461315</v>
       </c>
       <c r="R45" t="n">
-        <v>7064993</v>
+        <v>7064474</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5355,7 +5348,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822511</v>
+        <v>119822504</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5395,10 +5388,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461559</v>
+        <v>461951</v>
       </c>
       <c r="R46" t="n">
-        <v>7064334</v>
+        <v>7064993</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5462,10 +5455,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822527</v>
+        <v>119822539</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5474,20 +5467,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5495,17 +5488,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461315</v>
+        <v>461525</v>
       </c>
       <c r="R47" t="n">
-        <v>7064474</v>
+        <v>7064452</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5538,11 +5543,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822533</v>
+        <v>119822526</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461336</v>
+        <v>461252</v>
       </c>
       <c r="R4" t="n">
-        <v>7064553</v>
+        <v>7064479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822526</v>
+        <v>119822533</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461252</v>
+        <v>461336</v>
       </c>
       <c r="R5" t="n">
-        <v>7064479</v>
+        <v>7064553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822521</v>
+        <v>119822503</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461214</v>
+        <v>461856</v>
       </c>
       <c r="R15" t="n">
-        <v>7064209</v>
+        <v>7065027</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822503</v>
+        <v>119822537</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461856</v>
+        <v>461313</v>
       </c>
       <c r="R16" t="n">
-        <v>7065027</v>
+        <v>7064604</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822537</v>
+        <v>119822521</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461313</v>
+        <v>461214</v>
       </c>
       <c r="R17" t="n">
-        <v>7064604</v>
+        <v>7064209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2703,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822542</v>
+        <v>119822498</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461534</v>
+        <v>461417</v>
       </c>
       <c r="R21" t="n">
-        <v>7064335</v>
+        <v>7064708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2779,6 +2779,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822498</v>
+        <v>119822522</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2845,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461417</v>
+        <v>461156</v>
       </c>
       <c r="R22" t="n">
-        <v>7064708</v>
+        <v>7064289</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,7 +2917,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822522</v>
+        <v>119822531</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2952,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461156</v>
+        <v>461347</v>
       </c>
       <c r="R23" t="n">
-        <v>7064289</v>
+        <v>7064491</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2997,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822531</v>
+        <v>119822542</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461347</v>
+        <v>461534</v>
       </c>
       <c r="R24" t="n">
-        <v>7064491</v>
+        <v>7064335</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,11 +3100,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4813,7 +4813,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822500</v>
+        <v>119822505</v>
       </c>
       <c r="B41" t="n">
         <v>57310</v>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461569</v>
+        <v>461847</v>
       </c>
       <c r="R41" t="n">
-        <v>7065017</v>
+        <v>7064897</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,7 +4920,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822505</v>
+        <v>119822524</v>
       </c>
       <c r="B42" t="n">
         <v>57310</v>
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461847</v>
+        <v>461256</v>
       </c>
       <c r="R42" t="n">
-        <v>7064897</v>
+        <v>7064474</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822524</v>
+        <v>119822500</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461256</v>
+        <v>461569</v>
       </c>
       <c r="R43" t="n">
-        <v>7064474</v>
+        <v>7065017</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5134,10 +5134,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822511</v>
+        <v>119822539</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5167,17 +5167,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461559</v>
+        <v>461525</v>
       </c>
       <c r="R44" t="n">
-        <v>7064334</v>
+        <v>7064452</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5210,11 +5222,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5241,7 +5248,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822527</v>
+        <v>119822504</v>
       </c>
       <c r="B45" t="n">
         <v>57310</v>
@@ -5281,10 +5288,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461315</v>
+        <v>461951</v>
       </c>
       <c r="R45" t="n">
-        <v>7064474</v>
+        <v>7064993</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5348,7 +5355,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822504</v>
+        <v>119822511</v>
       </c>
       <c r="B46" t="n">
         <v>57310</v>
@@ -5388,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461951</v>
+        <v>461559</v>
       </c>
       <c r="R46" t="n">
-        <v>7064993</v>
+        <v>7064334</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5455,10 +5462,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822539</v>
+        <v>119822527</v>
       </c>
       <c r="B47" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5467,20 +5474,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5488,29 +5495,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461525</v>
+        <v>461315</v>
       </c>
       <c r="R47" t="n">
-        <v>7064452</v>
+        <v>7064474</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5543,6 +5538,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822503</v>
+        <v>119822521</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461856</v>
+        <v>461214</v>
       </c>
       <c r="R15" t="n">
-        <v>7065027</v>
+        <v>7064209</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822537</v>
+        <v>119822503</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461313</v>
+        <v>461856</v>
       </c>
       <c r="R16" t="n">
-        <v>7064604</v>
+        <v>7065027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822521</v>
+        <v>119822537</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461214</v>
+        <v>461313</v>
       </c>
       <c r="R17" t="n">
-        <v>7064209</v>
+        <v>7064604</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822526</v>
+        <v>119822533</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461252</v>
+        <v>461336</v>
       </c>
       <c r="R4" t="n">
-        <v>7064479</v>
+        <v>7064553</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822533</v>
+        <v>119822526</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461336</v>
+        <v>461252</v>
       </c>
       <c r="R5" t="n">
-        <v>7064553</v>
+        <v>7064479</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822521</v>
+        <v>119822503</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461214</v>
+        <v>461856</v>
       </c>
       <c r="R15" t="n">
-        <v>7064209</v>
+        <v>7065027</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822503</v>
+        <v>119822537</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461856</v>
+        <v>461313</v>
       </c>
       <c r="R16" t="n">
-        <v>7065027</v>
+        <v>7064604</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822537</v>
+        <v>119822521</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461313</v>
+        <v>461214</v>
       </c>
       <c r="R17" t="n">
-        <v>7064604</v>
+        <v>7064209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119822507</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822514</v>
+        <v>119822513</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461475</v>
+        <v>461492</v>
       </c>
       <c r="R3" t="n">
-        <v>7064279</v>
+        <v>7064272</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822533</v>
+        <v>119822514</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461336</v>
+        <v>461475</v>
       </c>
       <c r="R4" t="n">
-        <v>7064553</v>
+        <v>7064279</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822526</v>
+        <v>119822545</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461252</v>
+        <v>461589</v>
       </c>
       <c r="R5" t="n">
-        <v>7064479</v>
+        <v>7064542</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822509</v>
+        <v>119822528</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461603</v>
+        <v>461314</v>
       </c>
       <c r="R6" t="n">
-        <v>7064451</v>
+        <v>7064456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822535</v>
+        <v>119822501</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461326</v>
+        <v>461668</v>
       </c>
       <c r="R7" t="n">
-        <v>7064610</v>
+        <v>7065012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822530</v>
+        <v>119822538</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461353</v>
+        <v>461306</v>
       </c>
       <c r="R8" t="n">
-        <v>7064480</v>
+        <v>7064614</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822544</v>
+        <v>119822502</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461853</v>
+        <v>461858</v>
       </c>
       <c r="R9" t="n">
-        <v>7064648</v>
+        <v>7065038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822510</v>
+        <v>119822518</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461551</v>
+        <v>461326</v>
       </c>
       <c r="R10" t="n">
-        <v>7064346</v>
+        <v>7064274</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822528</v>
+        <v>119822541</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461314</v>
+        <v>461873</v>
       </c>
       <c r="R11" t="n">
-        <v>7064456</v>
+        <v>7065016</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822536</v>
+        <v>119822508</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461326</v>
+        <v>461571</v>
       </c>
       <c r="R12" t="n">
-        <v>7064600</v>
+        <v>7064490</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822502</v>
+        <v>119822523</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461858</v>
+        <v>461217</v>
       </c>
       <c r="R13" t="n">
-        <v>7065038</v>
+        <v>7064345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822515</v>
+        <v>119822506</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461455</v>
+        <v>461650</v>
       </c>
       <c r="R14" t="n">
-        <v>7064272</v>
+        <v>7064593</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822503</v>
+        <v>119822534</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461856</v>
+        <v>461337</v>
       </c>
       <c r="R15" t="n">
-        <v>7065027</v>
+        <v>7064589</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822537</v>
+        <v>119822521</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461313</v>
+        <v>461214</v>
       </c>
       <c r="R16" t="n">
-        <v>7064604</v>
+        <v>7064209</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822521</v>
+        <v>119822529</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461214</v>
+        <v>461336</v>
       </c>
       <c r="R17" t="n">
-        <v>7064209</v>
+        <v>7064457</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822508</v>
+        <v>119822500</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461571</v>
+        <v>461569</v>
       </c>
       <c r="R18" t="n">
-        <v>7064490</v>
+        <v>7065017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822520</v>
+        <v>119822540</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,21 +2500,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461287</v>
+        <v>461816</v>
       </c>
       <c r="R19" t="n">
-        <v>7064267</v>
+        <v>7065029</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,7 +2589,7 @@
         <v>119822499</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822498</v>
+        <v>119822533</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461417</v>
+        <v>461336</v>
       </c>
       <c r="R21" t="n">
-        <v>7064708</v>
+        <v>7064553</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822522</v>
+        <v>119822511</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2850,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461156</v>
+        <v>461559</v>
       </c>
       <c r="R22" t="n">
-        <v>7064289</v>
+        <v>7064334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822531</v>
+        <v>119822509</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461347</v>
+        <v>461603</v>
       </c>
       <c r="R23" t="n">
-        <v>7064491</v>
+        <v>7064451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +3017,7 @@
         <v>119822542</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822517</v>
+        <v>119822535</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461341</v>
+        <v>461326</v>
       </c>
       <c r="R25" t="n">
-        <v>7064286</v>
+        <v>7064610</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822545</v>
+        <v>119822524</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3273,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461589</v>
+        <v>461256</v>
       </c>
       <c r="R26" t="n">
-        <v>7064542</v>
+        <v>7064474</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3309,6 +3299,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822529</v>
+        <v>119822543</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461336</v>
+        <v>461512</v>
       </c>
       <c r="R27" t="n">
-        <v>7064457</v>
+        <v>7064795</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,11 +3406,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822519</v>
+        <v>119822530</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3482,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461301</v>
+        <v>461353</v>
       </c>
       <c r="R28" t="n">
-        <v>7064270</v>
+        <v>7064480</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3512,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822516</v>
+        <v>119822537</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461443</v>
+        <v>461313</v>
       </c>
       <c r="R29" t="n">
-        <v>7064240</v>
+        <v>7064604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3619,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,10 +3646,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822513</v>
+        <v>119822527</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3696,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461492</v>
+        <v>461315</v>
       </c>
       <c r="R30" t="n">
-        <v>7064272</v>
+        <v>7064474</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3726,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822523</v>
+        <v>119822517</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3803,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461217</v>
+        <v>461341</v>
       </c>
       <c r="R31" t="n">
-        <v>7064345</v>
+        <v>7064286</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3833,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3870,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822501</v>
+        <v>119822544</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,21 +3876,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461668</v>
+        <v>461853</v>
       </c>
       <c r="R32" t="n">
-        <v>7065012</v>
+        <v>7064648</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3946,11 +3936,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3977,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822518</v>
+        <v>119822503</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4017,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461326</v>
+        <v>461856</v>
       </c>
       <c r="R33" t="n">
-        <v>7064274</v>
+        <v>7065027</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4084,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822541</v>
+        <v>119822522</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4100,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4124,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461873</v>
+        <v>461156</v>
       </c>
       <c r="R34" t="n">
-        <v>7065016</v>
+        <v>7064289</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4160,6 +4145,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4186,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822506</v>
+        <v>119822498</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4226,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461650</v>
+        <v>461417</v>
       </c>
       <c r="R35" t="n">
-        <v>7064593</v>
+        <v>7064708</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4256,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822497</v>
+        <v>119822519</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4309,21 +4299,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4333,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461316</v>
+        <v>461301</v>
       </c>
       <c r="R36" t="n">
-        <v>7064356</v>
+        <v>7064270</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4369,6 +4359,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822543</v>
+        <v>119822515</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,21 +4406,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4435,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461512</v>
+        <v>461455</v>
       </c>
       <c r="R37" t="n">
-        <v>7064795</v>
+        <v>7064272</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,6 +4466,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822534</v>
+        <v>119822536</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461337</v>
+        <v>461326</v>
       </c>
       <c r="R38" t="n">
-        <v>7064589</v>
+        <v>7064600</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,10 +4604,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822538</v>
+        <v>119822526</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461306</v>
+        <v>461252</v>
       </c>
       <c r="R39" t="n">
-        <v>7064614</v>
+        <v>7064479</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822540</v>
+        <v>119822516</v>
       </c>
       <c r="B40" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461816</v>
+        <v>461443</v>
       </c>
       <c r="R40" t="n">
-        <v>7065029</v>
+        <v>7064240</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4787,6 +4787,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4813,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822505</v>
+        <v>119822510</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4853,10 +4858,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461847</v>
+        <v>461551</v>
       </c>
       <c r="R41" t="n">
-        <v>7064897</v>
+        <v>7064346</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4893,7 +4898,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4920,10 +4925,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822524</v>
+        <v>119822539</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>57431</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4932,20 +4937,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4953,17 +4958,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461256</v>
+        <v>461525</v>
       </c>
       <c r="R42" t="n">
-        <v>7064474</v>
+        <v>7064452</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4996,11 +5013,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5027,10 +5039,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822500</v>
+        <v>119822497</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5043,21 +5055,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5067,10 +5079,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461569</v>
+        <v>461316</v>
       </c>
       <c r="R43" t="n">
-        <v>7065017</v>
+        <v>7064356</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5103,11 +5115,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5134,10 +5141,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822539</v>
+        <v>119822520</v>
       </c>
       <c r="B44" t="n">
-        <v>57421</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5146,20 +5153,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5167,29 +5174,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461525</v>
+        <v>461287</v>
       </c>
       <c r="R44" t="n">
-        <v>7064452</v>
+        <v>7064267</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5222,6 +5217,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5248,10 +5248,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822504</v>
+        <v>119822505</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5288,10 +5288,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461951</v>
+        <v>461847</v>
       </c>
       <c r="R45" t="n">
-        <v>7064993</v>
+        <v>7064897</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822511</v>
+        <v>119822531</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461559</v>
+        <v>461347</v>
       </c>
       <c r="R46" t="n">
-        <v>7064334</v>
+        <v>7064491</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5462,10 +5462,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822527</v>
+        <v>119822504</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461315</v>
+        <v>461951</v>
       </c>
       <c r="R47" t="n">
-        <v>7064474</v>
+        <v>7064993</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822507</v>
+        <v>119822545</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461560</v>
+        <v>461589</v>
       </c>
       <c r="R2" t="n">
-        <v>7064491</v>
+        <v>7064542</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822513</v>
+        <v>119822507</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461492</v>
+        <v>461560</v>
       </c>
       <c r="R3" t="n">
-        <v>7064272</v>
+        <v>7064491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822514</v>
+        <v>119822513</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461475</v>
+        <v>461492</v>
       </c>
       <c r="R4" t="n">
-        <v>7064279</v>
+        <v>7064272</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822545</v>
+        <v>119822514</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461589</v>
+        <v>461475</v>
       </c>
       <c r="R5" t="n">
-        <v>7064542</v>
+        <v>7064279</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822528</v>
+        <v>119822501</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461314</v>
+        <v>461668</v>
       </c>
       <c r="R6" t="n">
-        <v>7064456</v>
+        <v>7065012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822501</v>
+        <v>119822528</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461668</v>
+        <v>461314</v>
       </c>
       <c r="R7" t="n">
-        <v>7065012</v>
+        <v>7064456</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822523</v>
+        <v>119822540</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461217</v>
+        <v>461816</v>
       </c>
       <c r="R13" t="n">
-        <v>7064345</v>
+        <v>7065029</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822506</v>
+        <v>119822523</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461650</v>
+        <v>461217</v>
       </c>
       <c r="R14" t="n">
-        <v>7064593</v>
+        <v>7064345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822534</v>
+        <v>119822506</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461337</v>
+        <v>461650</v>
       </c>
       <c r="R15" t="n">
-        <v>7064589</v>
+        <v>7064593</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822521</v>
+        <v>119822534</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461214</v>
+        <v>461337</v>
       </c>
       <c r="R16" t="n">
-        <v>7064209</v>
+        <v>7064589</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822529</v>
+        <v>119822521</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461336</v>
+        <v>461214</v>
       </c>
       <c r="R17" t="n">
-        <v>7064457</v>
+        <v>7064209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822500</v>
+        <v>119822529</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2417,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461569</v>
+        <v>461336</v>
       </c>
       <c r="R18" t="n">
-        <v>7065017</v>
+        <v>7064457</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822540</v>
+        <v>119822500</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461816</v>
+        <v>461569</v>
       </c>
       <c r="R19" t="n">
-        <v>7065029</v>
+        <v>7065017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822535</v>
+        <v>119822543</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461326</v>
+        <v>461512</v>
       </c>
       <c r="R25" t="n">
-        <v>7064610</v>
+        <v>7064795</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,11 +3192,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,7 +3218,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822524</v>
+        <v>119822535</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3263,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461256</v>
+        <v>461326</v>
       </c>
       <c r="R26" t="n">
-        <v>7064474</v>
+        <v>7064610</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3298,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822543</v>
+        <v>119822524</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,21 +3341,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461512</v>
+        <v>461256</v>
       </c>
       <c r="R27" t="n">
-        <v>7064795</v>
+        <v>7064474</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,6 +3401,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5248,7 +5248,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822505</v>
+        <v>119822504</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5288,10 +5288,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461847</v>
+        <v>461951</v>
       </c>
       <c r="R45" t="n">
-        <v>7064897</v>
+        <v>7064993</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5355,7 +5355,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822531</v>
+        <v>119822505</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461347</v>
+        <v>461847</v>
       </c>
       <c r="R46" t="n">
-        <v>7064491</v>
+        <v>7064897</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822504</v>
+        <v>119822531</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461951</v>
+        <v>461347</v>
       </c>
       <c r="R47" t="n">
-        <v>7064993</v>
+        <v>7064491</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822545</v>
+        <v>119822538</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461589</v>
+        <v>461306</v>
       </c>
       <c r="R2" t="n">
-        <v>7064542</v>
+        <v>7064614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822507</v>
+        <v>119822545</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461560</v>
+        <v>461589</v>
       </c>
       <c r="R3" t="n">
-        <v>7064491</v>
+        <v>7064542</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822513</v>
+        <v>119822528</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461492</v>
+        <v>461314</v>
       </c>
       <c r="R4" t="n">
-        <v>7064272</v>
+        <v>7064456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822514</v>
+        <v>119822536</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461475</v>
+        <v>461326</v>
       </c>
       <c r="R5" t="n">
-        <v>7064279</v>
+        <v>7064600</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822501</v>
+        <v>119822529</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461668</v>
+        <v>461336</v>
       </c>
       <c r="R6" t="n">
-        <v>7065012</v>
+        <v>7064457</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822528</v>
+        <v>119822537</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461314</v>
+        <v>461313</v>
       </c>
       <c r="R7" t="n">
-        <v>7064456</v>
+        <v>7064604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822538</v>
+        <v>119822521</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461306</v>
+        <v>461214</v>
       </c>
       <c r="R8" t="n">
-        <v>7064614</v>
+        <v>7064209</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822502</v>
+        <v>119822524</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461858</v>
+        <v>461256</v>
       </c>
       <c r="R9" t="n">
-        <v>7065038</v>
+        <v>7064474</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822518</v>
+        <v>119822542</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461326</v>
+        <v>461534</v>
       </c>
       <c r="R10" t="n">
-        <v>7064274</v>
+        <v>7064335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822541</v>
+        <v>119822516</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461873</v>
+        <v>461443</v>
       </c>
       <c r="R11" t="n">
-        <v>7065016</v>
+        <v>7064240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822508</v>
+        <v>119822505</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461571</v>
+        <v>461847</v>
       </c>
       <c r="R12" t="n">
-        <v>7064490</v>
+        <v>7064897</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822540</v>
+        <v>119822518</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461816</v>
+        <v>461326</v>
       </c>
       <c r="R13" t="n">
-        <v>7065029</v>
+        <v>7064274</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119822523</v>
+        <v>119822534</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1984,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461217</v>
+        <v>461337</v>
       </c>
       <c r="R14" t="n">
-        <v>7064345</v>
+        <v>7064589</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822506</v>
+        <v>119822530</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461650</v>
+        <v>461353</v>
       </c>
       <c r="R15" t="n">
-        <v>7064593</v>
+        <v>7064480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822534</v>
+        <v>119822513</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461337</v>
+        <v>461492</v>
       </c>
       <c r="R16" t="n">
-        <v>7064589</v>
+        <v>7064272</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822521</v>
+        <v>119822499</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2305,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461214</v>
+        <v>461452</v>
       </c>
       <c r="R17" t="n">
-        <v>7064209</v>
+        <v>7064801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822529</v>
+        <v>119822535</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2412,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461336</v>
+        <v>461326</v>
       </c>
       <c r="R18" t="n">
-        <v>7064457</v>
+        <v>7064610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822500</v>
+        <v>119822520</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461569</v>
+        <v>461287</v>
       </c>
       <c r="R19" t="n">
-        <v>7065017</v>
+        <v>7064267</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822499</v>
+        <v>119822517</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2626,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461452</v>
+        <v>461341</v>
       </c>
       <c r="R20" t="n">
-        <v>7064801</v>
+        <v>7064286</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822533</v>
+        <v>119822510</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461336</v>
+        <v>461551</v>
       </c>
       <c r="R21" t="n">
-        <v>7064553</v>
+        <v>7064346</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822511</v>
+        <v>119822497</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461559</v>
+        <v>461316</v>
       </c>
       <c r="R22" t="n">
-        <v>7064334</v>
+        <v>7064356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,11 +2881,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822509</v>
+        <v>119822540</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461603</v>
+        <v>461816</v>
       </c>
       <c r="R23" t="n">
-        <v>7064451</v>
+        <v>7065029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,11 +2983,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822542</v>
+        <v>119822519</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461534</v>
+        <v>461301</v>
       </c>
       <c r="R24" t="n">
-        <v>7064335</v>
+        <v>7064270</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,6 +3085,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822543</v>
+        <v>119822508</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461512</v>
+        <v>461571</v>
       </c>
       <c r="R25" t="n">
-        <v>7064795</v>
+        <v>7064490</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,6 +3192,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822535</v>
+        <v>119822501</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3258,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461326</v>
+        <v>461668</v>
       </c>
       <c r="R26" t="n">
-        <v>7064610</v>
+        <v>7065012</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3303,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822524</v>
+        <v>119822527</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3365,7 +3370,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461256</v>
+        <v>461315</v>
       </c>
       <c r="R27" t="n">
         <v>7064474</v>
@@ -3432,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822530</v>
+        <v>119822539</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3444,20 +3449,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3465,17 +3470,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461353</v>
+        <v>461525</v>
       </c>
       <c r="R28" t="n">
-        <v>7064480</v>
+        <v>7064452</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3508,11 +3525,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,7 +3551,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822537</v>
+        <v>119822498</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3579,10 +3591,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461313</v>
+        <v>461417</v>
       </c>
       <c r="R29" t="n">
-        <v>7064604</v>
+        <v>7064708</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3631,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,7 +3658,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822527</v>
+        <v>119822522</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3686,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461315</v>
+        <v>461156</v>
       </c>
       <c r="R30" t="n">
-        <v>7064474</v>
+        <v>7064289</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3726,7 +3738,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,7 +3765,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822517</v>
+        <v>119822533</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3793,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461341</v>
+        <v>461336</v>
       </c>
       <c r="R31" t="n">
-        <v>7064286</v>
+        <v>7064553</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,7 +3845,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822544</v>
+        <v>119822502</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3876,21 +3888,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461853</v>
+        <v>461858</v>
       </c>
       <c r="R32" t="n">
-        <v>7064648</v>
+        <v>7065038</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3936,6 +3948,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,7 +3979,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822503</v>
+        <v>119822504</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4002,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461856</v>
+        <v>461951</v>
       </c>
       <c r="R33" t="n">
-        <v>7065027</v>
+        <v>7064993</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4069,7 +4086,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822522</v>
+        <v>119822509</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4109,10 +4126,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461156</v>
+        <v>461603</v>
       </c>
       <c r="R34" t="n">
-        <v>7064289</v>
+        <v>7064451</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,7 +4166,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,10 +4193,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822498</v>
+        <v>119822541</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,21 +4209,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4233,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461417</v>
+        <v>461873</v>
       </c>
       <c r="R35" t="n">
-        <v>7064708</v>
+        <v>7065016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4252,11 +4269,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,10 +4295,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822519</v>
+        <v>119822543</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4299,21 +4311,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4323,10 +4335,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461301</v>
+        <v>461512</v>
       </c>
       <c r="R36" t="n">
-        <v>7064270</v>
+        <v>7064795</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4359,11 +4371,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,10 +4397,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822515</v>
+        <v>119822544</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4406,21 +4413,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4430,10 +4437,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461455</v>
+        <v>461853</v>
       </c>
       <c r="R37" t="n">
-        <v>7064272</v>
+        <v>7064648</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4466,11 +4473,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,7 +4499,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822536</v>
+        <v>119822507</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4537,10 +4539,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461326</v>
+        <v>461560</v>
       </c>
       <c r="R38" t="n">
-        <v>7064600</v>
+        <v>7064491</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4604,7 +4606,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822526</v>
+        <v>119822503</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4644,10 +4646,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461252</v>
+        <v>461856</v>
       </c>
       <c r="R39" t="n">
-        <v>7064479</v>
+        <v>7065027</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,7 +4713,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822516</v>
+        <v>119822506</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4751,10 +4753,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461443</v>
+        <v>461650</v>
       </c>
       <c r="R40" t="n">
-        <v>7064240</v>
+        <v>7064593</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4791,7 +4793,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,7 +4820,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822510</v>
+        <v>119822515</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4858,10 +4860,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461551</v>
+        <v>461455</v>
       </c>
       <c r="R41" t="n">
-        <v>7064346</v>
+        <v>7064272</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4925,10 +4927,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822539</v>
+        <v>119822526</v>
       </c>
       <c r="B42" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4937,20 +4939,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4958,29 +4960,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461525</v>
+        <v>461252</v>
       </c>
       <c r="R42" t="n">
-        <v>7064452</v>
+        <v>7064479</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5013,6 +5003,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5039,10 +5034,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822497</v>
+        <v>119822514</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5055,21 +5050,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5079,10 +5074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461316</v>
+        <v>461475</v>
       </c>
       <c r="R43" t="n">
-        <v>7064356</v>
+        <v>7064279</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5115,6 +5110,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5141,7 +5141,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822520</v>
+        <v>119822523</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461287</v>
+        <v>461217</v>
       </c>
       <c r="R44" t="n">
-        <v>7064267</v>
+        <v>7064345</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5248,7 +5248,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822504</v>
+        <v>119822531</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5288,10 +5288,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461951</v>
+        <v>461347</v>
       </c>
       <c r="R45" t="n">
-        <v>7064993</v>
+        <v>7064491</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5355,7 +5355,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822505</v>
+        <v>119822500</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461847</v>
+        <v>461569</v>
       </c>
       <c r="R46" t="n">
-        <v>7064897</v>
+        <v>7065017</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822531</v>
+        <v>119822511</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461347</v>
+        <v>461559</v>
       </c>
       <c r="R47" t="n">
-        <v>7064491</v>
+        <v>7064334</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822497</v>
+        <v>119822519</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461316</v>
+        <v>461301</v>
       </c>
       <c r="R22" t="n">
-        <v>7064356</v>
+        <v>7064270</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,6 +2881,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822540</v>
+        <v>119822497</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2928,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461816</v>
+        <v>461316</v>
       </c>
       <c r="R23" t="n">
-        <v>7065029</v>
+        <v>7064356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822519</v>
+        <v>119822540</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461301</v>
+        <v>461816</v>
       </c>
       <c r="R24" t="n">
-        <v>7064270</v>
+        <v>7065029</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,11 +3090,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822508</v>
+        <v>119822539</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3128,20 +3128,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3149,17 +3149,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461571</v>
+        <v>461525</v>
       </c>
       <c r="R25" t="n">
-        <v>7064490</v>
+        <v>7064452</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,11 +3204,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,7 +3230,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822501</v>
+        <v>119822508</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3263,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461668</v>
+        <v>461571</v>
       </c>
       <c r="R26" t="n">
-        <v>7065012</v>
+        <v>7064490</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3310,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,7 +3337,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822527</v>
+        <v>119822501</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3370,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461315</v>
+        <v>461668</v>
       </c>
       <c r="R27" t="n">
-        <v>7064474</v>
+        <v>7065012</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,10 +3444,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822539</v>
+        <v>119822527</v>
       </c>
       <c r="B28" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3449,20 +3456,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3470,29 +3477,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461525</v>
+        <v>461315</v>
       </c>
       <c r="R28" t="n">
-        <v>7064452</v>
+        <v>7064474</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,6 +3520,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3872,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822502</v>
+        <v>119822541</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461858</v>
+        <v>461873</v>
       </c>
       <c r="R32" t="n">
-        <v>7065038</v>
+        <v>7065016</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3948,11 +3948,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3979,7 +3974,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822504</v>
+        <v>119822502</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4019,10 +4014,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461951</v>
+        <v>461858</v>
       </c>
       <c r="R33" t="n">
-        <v>7064993</v>
+        <v>7065038</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,7 +4081,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822509</v>
+        <v>119822504</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4126,10 +4121,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461603</v>
+        <v>461951</v>
       </c>
       <c r="R34" t="n">
-        <v>7064451</v>
+        <v>7064993</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822541</v>
+        <v>119822509</v>
       </c>
       <c r="B35" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4209,21 +4204,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4233,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461873</v>
+        <v>461603</v>
       </c>
       <c r="R35" t="n">
-        <v>7065016</v>
+        <v>7064451</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4269,6 +4264,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 26256-2024 artfynd.xlsx
+++ b/artfynd/A 26256-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822538</v>
+        <v>119822529</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461306</v>
+        <v>461336</v>
       </c>
       <c r="R2" t="n">
-        <v>7064614</v>
+        <v>7064457</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822545</v>
+        <v>119822541</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461589</v>
+        <v>461873</v>
       </c>
       <c r="R3" t="n">
-        <v>7064542</v>
+        <v>7065016</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822528</v>
+        <v>119822523</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461314</v>
+        <v>461217</v>
       </c>
       <c r="R4" t="n">
-        <v>7064456</v>
+        <v>7064345</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822536</v>
+        <v>119822533</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461326</v>
+        <v>461336</v>
       </c>
       <c r="R5" t="n">
-        <v>7064600</v>
+        <v>7064553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822529</v>
+        <v>119822502</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461336</v>
+        <v>461858</v>
       </c>
       <c r="R6" t="n">
-        <v>7064457</v>
+        <v>7065038</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822537</v>
+        <v>119822515</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461313</v>
+        <v>461455</v>
       </c>
       <c r="R7" t="n">
-        <v>7064604</v>
+        <v>7064272</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119822521</v>
+        <v>119822535</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461214</v>
+        <v>461326</v>
       </c>
       <c r="R8" t="n">
-        <v>7064209</v>
+        <v>7064610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119822524</v>
+        <v>119822505</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461256</v>
+        <v>461847</v>
       </c>
       <c r="R9" t="n">
-        <v>7064474</v>
+        <v>7064897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119822542</v>
+        <v>119822508</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461534</v>
+        <v>461571</v>
       </c>
       <c r="R10" t="n">
-        <v>7064335</v>
+        <v>7064490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119822516</v>
+        <v>119822542</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461443</v>
+        <v>461534</v>
       </c>
       <c r="R11" t="n">
-        <v>7064240</v>
+        <v>7064335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119822505</v>
+        <v>119822536</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461847</v>
+        <v>461326</v>
       </c>
       <c r="R12" t="n">
-        <v>7064897</v>
+        <v>7064600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119822518</v>
+        <v>119822498</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461326</v>
+        <v>461417</v>
       </c>
       <c r="R13" t="n">
-        <v>7064274</v>
+        <v>7064708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119822530</v>
+        <v>119822528</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461353</v>
+        <v>461314</v>
       </c>
       <c r="R15" t="n">
-        <v>7064480</v>
+        <v>7064456</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119822513</v>
+        <v>119822501</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461492</v>
+        <v>461668</v>
       </c>
       <c r="R16" t="n">
-        <v>7064272</v>
+        <v>7065012</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119822499</v>
+        <v>119822497</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461452</v>
+        <v>461316</v>
       </c>
       <c r="R17" t="n">
-        <v>7064801</v>
+        <v>7064356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,11 +2346,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119822535</v>
+        <v>119822513</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2417,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461326</v>
+        <v>461492</v>
       </c>
       <c r="R18" t="n">
-        <v>7064610</v>
+        <v>7064272</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119822520</v>
+        <v>119822531</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461287</v>
+        <v>461347</v>
       </c>
       <c r="R19" t="n">
-        <v>7064267</v>
+        <v>7064491</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119822517</v>
+        <v>119822499</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2631,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461341</v>
+        <v>461452</v>
       </c>
       <c r="R20" t="n">
-        <v>7064286</v>
+        <v>7064801</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119822510</v>
+        <v>119822506</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461551</v>
+        <v>461650</v>
       </c>
       <c r="R21" t="n">
-        <v>7064346</v>
+        <v>7064593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119822519</v>
+        <v>119822524</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2845,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461301</v>
+        <v>461256</v>
       </c>
       <c r="R22" t="n">
-        <v>7064270</v>
+        <v>7064474</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119822497</v>
+        <v>119822537</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461316</v>
+        <v>461313</v>
       </c>
       <c r="R23" t="n">
-        <v>7064356</v>
+        <v>7064604</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,6 +2983,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119822540</v>
+        <v>119822543</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461816</v>
+        <v>461512</v>
       </c>
       <c r="R24" t="n">
-        <v>7065029</v>
+        <v>7064795</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119822539</v>
+        <v>119822510</v>
       </c>
       <c r="B25" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3128,20 +3128,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3149,29 +3149,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461525</v>
+        <v>461551</v>
       </c>
       <c r="R25" t="n">
-        <v>7064452</v>
+        <v>7064346</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,6 +3192,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3230,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119822508</v>
+        <v>119822509</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3270,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461571</v>
+        <v>461603</v>
       </c>
       <c r="R26" t="n">
-        <v>7064490</v>
+        <v>7064451</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,7 +3303,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3337,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119822501</v>
+        <v>119822516</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3377,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461668</v>
+        <v>461443</v>
       </c>
       <c r="R27" t="n">
-        <v>7065012</v>
+        <v>7064240</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3444,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119822527</v>
+        <v>119822504</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3484,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461315</v>
+        <v>461951</v>
       </c>
       <c r="R28" t="n">
-        <v>7064474</v>
+        <v>7064993</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119822498</v>
+        <v>119822544</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3567,21 +3560,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3591,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461417</v>
+        <v>461853</v>
       </c>
       <c r="R29" t="n">
-        <v>7064708</v>
+        <v>7064648</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3627,11 +3620,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3658,7 +3646,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119822522</v>
+        <v>119822526</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3698,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461156</v>
+        <v>461252</v>
       </c>
       <c r="R30" t="n">
-        <v>7064289</v>
+        <v>7064479</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,7 +3726,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119822533</v>
+        <v>119822514</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3805,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461336</v>
+        <v>461475</v>
       </c>
       <c r="R31" t="n">
-        <v>7064553</v>
+        <v>7064279</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3845,7 +3833,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3872,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119822541</v>
+        <v>119822522</v>
       </c>
       <c r="B32" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3888,21 +3876,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3912,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461873</v>
+        <v>461156</v>
       </c>
       <c r="R32" t="n">
-        <v>7065016</v>
+        <v>7064289</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3948,6 +3936,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3974,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119822502</v>
+        <v>119822511</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4014,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461858</v>
+        <v>461559</v>
       </c>
       <c r="R33" t="n">
-        <v>7065038</v>
+        <v>7064334</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4081,7 +4074,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119822504</v>
+        <v>119822520</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4121,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461951</v>
+        <v>461287</v>
       </c>
       <c r="R34" t="n">
-        <v>7064993</v>
+        <v>7064267</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,7 +4181,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119822509</v>
+        <v>119822518</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4228,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461603</v>
+        <v>461326</v>
       </c>
       <c r="R35" t="n">
-        <v>7064451</v>
+        <v>7064274</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,7 +4288,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119822543</v>
+        <v>119822545</v>
       </c>
       <c r="B36" t="n">
         <v>78542</v>
@@ -4335,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461512</v>
+        <v>461589</v>
       </c>
       <c r="R36" t="n">
-        <v>7064795</v>
+        <v>7064542</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4397,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119822544</v>
+        <v>119822540</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4413,21 +4406,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4437,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461853</v>
+        <v>461816</v>
       </c>
       <c r="R37" t="n">
-        <v>7064648</v>
+        <v>7065029</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4499,7 +4492,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119822507</v>
+        <v>119822521</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4539,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461560</v>
+        <v>461214</v>
       </c>
       <c r="R38" t="n">
-        <v>7064491</v>
+        <v>7064209</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4579,7 +4572,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4606,7 +4599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119822503</v>
+        <v>119822519</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4646,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461856</v>
+        <v>461301</v>
       </c>
       <c r="R39" t="n">
-        <v>7065027</v>
+        <v>7064270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,7 +4679,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4713,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119822506</v>
+        <v>119822507</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4753,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461650</v>
+        <v>461560</v>
       </c>
       <c r="R40" t="n">
-        <v>7064593</v>
+        <v>7064491</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4793,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4820,7 +4813,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119822515</v>
+        <v>119822500</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4860,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461455</v>
+        <v>461569</v>
       </c>
       <c r="R41" t="n">
-        <v>7064272</v>
+        <v>7065017</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4900,7 +4893,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4927,7 +4920,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119822526</v>
+        <v>119822517</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4967,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461252</v>
+        <v>461341</v>
       </c>
       <c r="R42" t="n">
-        <v>7064479</v>
+        <v>7064286</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5007,7 +5000,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5034,7 +5027,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119822514</v>
+        <v>119822538</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5074,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461475</v>
+        <v>461306</v>
       </c>
       <c r="R43" t="n">
-        <v>7064279</v>
+        <v>7064614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5141,10 +5134,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119822523</v>
+        <v>119822539</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5153,20 +5146,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5174,17 +5167,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vallrun NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461217</v>
+        <v>461525</v>
       </c>
       <c r="R44" t="n">
-        <v>7064345</v>
+        <v>7064452</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5217,11 +5222,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5248,7 +5248,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119822531</v>
+        <v>119822503</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5288,10 +5288,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461347</v>
+        <v>461856</v>
       </c>
       <c r="R45" t="n">
-        <v>7064491</v>
+        <v>7065027</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5355,7 +5355,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119822500</v>
+        <v>119822530</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461569</v>
+        <v>461353</v>
       </c>
       <c r="R46" t="n">
-        <v>7065017</v>
+        <v>7064480</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5462,7 +5462,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119822511</v>
+        <v>119822527</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461559</v>
+        <v>461315</v>
       </c>
       <c r="R47" t="n">
-        <v>7064334</v>
+        <v>7064474</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
